--- a/inputs/data_symbols_TD/09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5.xlsx
+++ b/inputs/data_symbols_TD/09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C7AA94D-8DF2-40EE-B65A-33DF3025B12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE52137-A38E-4C85-9E5D-851FA496E29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{D43AE29B-EC06-4C5B-AC68-424A518DF6CF}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{8B319E7E-412A-4583-8BB2-F46E854D6610}"/>
   </bookViews>
   <sheets>
     <sheet name="09_LTAN06_800km_1213COLD_MX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC37B969-C921-40AF-AB3C-4600C170D04B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73319BF-E846-4CF9-A46D-60BC79E426BC}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>7.6576680000000001</v>
+        <v>34.571510000000004</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>7.6576680000000001</v>
+        <v>34.571510000000004</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>7.6523630000000002</v>
+        <v>34.566609999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>7.6473240000000002</v>
+        <v>34.562620000000003</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>7.6424570000000003</v>
+        <v>34.55941</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>7.6377189999999997</v>
+        <v>34.556930000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>7.6330799999999996</v>
+        <v>34.555140000000002</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>7.6285109999999996</v>
+        <v>34.554020000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>7.6240300000000003</v>
+        <v>34.553570000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>7.6196159999999997</v>
+        <v>34.553800000000003</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>7.615265</v>
+        <v>34.554690000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>7.6110030000000002</v>
+        <v>34.5563</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>7.6068020000000001</v>
+        <v>34.558610000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>7.6026429999999996</v>
+        <v>34.561630000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>7.598516</v>
+        <v>34.565370000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>7.5944180000000001</v>
+        <v>34.569850000000002</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>7.5903640000000001</v>
+        <v>34.575049999999997</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>7.5863589999999999</v>
+        <v>34.580979999999997</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>7.5823939999999999</v>
+        <v>34.58764</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>7.5780099999999999</v>
+        <v>34.592350000000003</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>7.5725959999999999</v>
+        <v>34.592619999999997</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>7.5661680000000002</v>
+        <v>34.588760000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>7.5587350000000004</v>
+        <v>34.580939999999998</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>7.5503070000000001</v>
+        <v>34.569290000000002</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>7.5408980000000003</v>
+        <v>34.553899999999999</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>7.5305340000000003</v>
+        <v>34.534829999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>7.5191990000000004</v>
+        <v>34.512099999999997</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>7.5068840000000003</v>
+        <v>34.48574</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>7.4935780000000003</v>
+        <v>34.455759999999998</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>7.4792550000000002</v>
+        <v>34.422130000000003</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>7.4639290000000003</v>
+        <v>34.384819999999998</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>7.4475819999999997</v>
+        <v>34.343800000000002</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>7.4301890000000004</v>
+        <v>34.299050000000001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>7.4117480000000002</v>
+        <v>34.250590000000003</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>7.3922559999999997</v>
+        <v>34.198419999999999</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>7.3717329999999999</v>
+        <v>34.142539999999997</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>7.3507379999999998</v>
+        <v>34.085279999999997</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>7.329777</v>
+        <v>34.028880000000001</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>7.3088410000000001</v>
+        <v>33.97325</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>7.2879430000000003</v>
+        <v>33.918329999999997</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>7.2670919999999999</v>
+        <v>33.864109999999997</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>7.2463490000000004</v>
+        <v>33.810659999999999</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>7.2257639999999999</v>
+        <v>33.758069999999996</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>7.205368</v>
+        <v>33.706400000000002</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>7.1852349999999996</v>
+        <v>33.655760000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>7.165413</v>
+        <v>33.606290000000001</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>7.1459489999999999</v>
+        <v>33.558109999999999</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>7.1269169999999997</v>
+        <v>33.511369999999999</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>7.1083600000000002</v>
+        <v>33.466209999999997</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>7.0903200000000002</v>
+        <v>33.42277</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>7.0728390000000001</v>
+        <v>33.381239999999998</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>7.0559580000000004</v>
+        <v>33.34169</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>7.0397939999999997</v>
+        <v>33.304220000000001</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>7.0244520000000001</v>
+        <v>33.268900000000002</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>7.0099460000000002</v>
+        <v>33.235790000000001</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>6.9966200000000001</v>
+        <v>33.205329999999996</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>6.984591</v>
+        <v>33.177630000000001</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>6.9738420000000003</v>
+        <v>33.152679999999997</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>6.9646660000000002</v>
+        <v>33.130830000000003</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>6.9570590000000001</v>
+        <v>33.112020000000001</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>6.9510459999999998</v>
+        <v>33.096200000000003</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>6.9468230000000002</v>
+        <v>33.083449999999999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>6.9443020000000004</v>
+        <v>33.073680000000003</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>6.9434230000000001</v>
+        <v>33.066830000000003</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>6.9441459999999999</v>
+        <v>33.062849999999997</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>6.9464360000000003</v>
+        <v>33.061700000000002</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>6.9501939999999998</v>
+        <v>33.06324</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>6.9553500000000001</v>
+        <v>33.067309999999999</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>6.9618779999999996</v>
+        <v>33.073830000000001</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>6.9695799999999997</v>
+        <v>33.082569999999997</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>6.9783840000000001</v>
+        <v>33.09348</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>6.9882359999999997</v>
+        <v>33.106450000000002</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>6.9986499999999996</v>
+        <v>33.12097</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>7.0096959999999999</v>
+        <v>33.137059999999998</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>7.0213070000000002</v>
+        <v>33.154620000000001</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>7.0332210000000002</v>
+        <v>33.173389999999998</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>7.0454540000000003</v>
+        <v>33.193280000000001</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>7.0578339999999997</v>
+        <v>33.213970000000003</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>7.0701970000000003</v>
+        <v>33.235190000000003</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>7.0825810000000002</v>
+        <v>33.257040000000003</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>7.0945650000000002</v>
+        <v>33.279269999999997</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>7.1060720000000002</v>
+        <v>33.301839999999999</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>7.1172000000000004</v>
+        <v>33.324770000000001</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>7.127745</v>
+        <v>33.347720000000002</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>7.1377810000000004</v>
+        <v>33.370699999999999</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>7.1473490000000002</v>
+        <v>33.393700000000003</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>7.156339</v>
+        <v>33.416530000000002</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>7.1647850000000002</v>
+        <v>33.439259999999997</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>7.1725880000000002</v>
+        <v>33.461840000000002</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>7.179602</v>
+        <v>33.484189999999998</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>7.185943</v>
+        <v>33.506320000000002</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>7.1917809999999998</v>
+        <v>33.528280000000002</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>7.1971889999999998</v>
+        <v>33.550109999999997</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>7.2021499999999996</v>
+        <v>33.571840000000002</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>7.2066660000000002</v>
+        <v>33.593620000000001</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>7.2107570000000001</v>
+        <v>33.61542</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>7.2144570000000003</v>
+        <v>33.637219999999999</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>7.2181309999999996</v>
+        <v>33.659300000000002</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>7.2217390000000004</v>
+        <v>33.681620000000002</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>7.2253619999999996</v>
+        <v>33.704270000000001</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>7.2292639999999997</v>
+        <v>33.727490000000003</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>7.233358</v>
+        <v>33.751199999999997</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>7.2377180000000001</v>
+        <v>33.775460000000002</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>7.2424220000000004</v>
+        <v>33.800330000000002</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>7.2474030000000003</v>
+        <v>33.825710000000001</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>7.2526149999999996</v>
+        <v>33.851550000000003</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>7.2580119999999999</v>
+        <v>33.877809999999997</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>7.2635430000000003</v>
+        <v>33.904429999999998</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>7.2691990000000004</v>
+        <v>33.93139</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>7.2749350000000002</v>
+        <v>33.958660000000002</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>7.2807190000000004</v>
+        <v>33.986199999999997</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>7.2865529999999996</v>
+        <v>34.014009999999999</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>7.2923850000000003</v>
+        <v>34.042059999999999</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>7.2981740000000004</v>
+        <v>34.070309999999999</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>7.3038920000000003</v>
+        <v>34.098770000000002</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>7.3095169999999996</v>
+        <v>34.127400000000002</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>7.315048</v>
+        <v>34.156190000000002</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>7.3204770000000003</v>
+        <v>34.185119999999998</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>7.3257849999999998</v>
+        <v>34.214170000000003</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>7.3304989999999997</v>
+        <v>34.240609999999997</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>7.3339970000000001</v>
+        <v>34.261940000000003</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>7.3362889999999998</v>
+        <v>34.278419999999997</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>7.3373790000000003</v>
+        <v>34.290300000000002</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>7.3372739999999999</v>
+        <v>34.29768</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>7.335985</v>
+        <v>34.300660000000001</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>7.333539</v>
+        <v>34.299309999999998</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>7.329917</v>
+        <v>34.293680000000002</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>7.3251119999999998</v>
+        <v>34.283790000000003</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>7.3191129999999998</v>
+        <v>34.269660000000002</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>7.3118970000000001</v>
+        <v>34.251289999999997</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>7.3034780000000001</v>
+        <v>34.228659999999998</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>7.2938419999999997</v>
+        <v>34.20176</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>7.2829670000000002</v>
+        <v>34.170569999999998</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>7.2708519999999996</v>
+        <v>34.135150000000003</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>7.2575000000000003</v>
+        <v>34.095500000000001</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>7.242934</v>
+        <v>34.051630000000003</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>7.2277170000000002</v>
+        <v>34.00591</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>7.2123629999999999</v>
+        <v>33.960619999999999</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>7.1968639999999997</v>
+        <v>33.915669999999999</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>7.1812379999999996</v>
+        <v>33.871009999999998</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>7.1654989999999996</v>
+        <v>33.826650000000001</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>7.1497099999999998</v>
+        <v>33.782670000000003</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>7.1339259999999998</v>
+        <v>33.739159999999998</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>7.1181809999999999</v>
+        <v>33.696219999999997</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>7.1025530000000003</v>
+        <v>33.653959999999998</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>7.0870949999999997</v>
+        <v>33.61251</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>7.0718569999999996</v>
+        <v>33.572020000000002</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>7.0569160000000002</v>
+        <v>33.53266</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>7.042319</v>
+        <v>33.49456</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>7.0281120000000001</v>
+        <v>33.457889999999999</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>7.0143409999999999</v>
+        <v>33.422829999999998</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>7.0010500000000002</v>
+        <v>33.389479999999999</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>6.988359</v>
+        <v>33.357930000000003</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>6.9763770000000003</v>
+        <v>33.328279999999999</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>6.9651209999999999</v>
+        <v>33.30059</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>6.9549380000000003</v>
+        <v>33.275300000000001</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>6.9459489999999997</v>
+        <v>33.252540000000003</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>6.9381389999999996</v>
+        <v>33.232309999999998</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>6.9318039999999996</v>
+        <v>33.214950000000002</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>6.9269439999999998</v>
+        <v>33.200429999999997</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>6.9235850000000001</v>
+        <v>33.188699999999997</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>6.9219290000000004</v>
+        <v>33.179839999999999</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>6.9218869999999999</v>
+        <v>33.173769999999998</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>6.9234039999999997</v>
+        <v>33.170450000000002</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>6.9264419999999998</v>
+        <v>33.169820000000001</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>6.930968</v>
+        <v>33.171849999999999</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>6.9368850000000002</v>
+        <v>33.176409999999997</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>6.9441269999999999</v>
+        <v>33.183349999999997</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>6.9526690000000002</v>
+        <v>33.19258</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>6.9623160000000004</v>
+        <v>33.203899999999997</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>6.9729970000000003</v>
+        <v>33.217239999999997</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>6.984661</v>
+        <v>33.232520000000001</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>6.996823</v>
+        <v>33.249209999999998</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>7.009557</v>
+        <v>33.267359999999996</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>7.0227969999999997</v>
+        <v>33.286859999999997</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>7.0362819999999999</v>
+        <v>33.30744</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>7.0500299999999996</v>
+        <v>33.329039999999999</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>7.0638719999999999</v>
+        <v>33.35134</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>7.0776450000000004</v>
+        <v>33.374079999999999</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>7.0913880000000002</v>
+        <v>33.397329999999997</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>7.1046820000000004</v>
+        <v>33.420879999999997</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>7.1174520000000001</v>
+        <v>33.444679999999998</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>7.1297969999999999</v>
+        <v>33.468760000000003</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>7.1415150000000001</v>
+        <v>33.49277</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>7.1526800000000001</v>
+        <v>33.516739999999999</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>7.1633370000000003</v>
+        <v>33.540649999999999</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>7.1733739999999999</v>
+        <v>33.564309999999999</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>7.18283</v>
+        <v>33.587809999999998</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>7.1916029999999997</v>
+        <v>33.6111</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>7.1995519999999997</v>
+        <v>33.634079999999997</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>7.2067920000000001</v>
+        <v>33.656790000000001</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>7.2134970000000003</v>
+        <v>33.679270000000002</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>7.2197370000000003</v>
+        <v>33.701560000000001</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>7.225498</v>
+        <v>33.723709999999997</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>7.2307829999999997</v>
+        <v>33.745849999999997</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>7.2356129999999999</v>
+        <v>33.767960000000002</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>7.2400229999999999</v>
+        <v>33.790019999999998</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>7.2443799999999996</v>
+        <v>33.81232</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>7.2486430000000004</v>
+        <v>33.834820000000001</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>7.2528940000000004</v>
+        <v>33.857610000000001</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>7.2573990000000004</v>
+        <v>33.880929999999999</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>7.2620719999999999</v>
+        <v>33.904699999999998</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>7.2669870000000003</v>
+        <v>33.928980000000003</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>7.2722220000000002</v>
+        <v>33.953830000000004</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>7.2777120000000002</v>
+        <v>33.979170000000003</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>7.2834120000000002</v>
+        <v>34.004939999999998</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>7.2892749999999999</v>
+        <v>34.031100000000002</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>7.2952519999999996</v>
+        <v>34.057580000000002</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>7.3013349999999999</v>
+        <v>34.084389999999999</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>7.30748</v>
+        <v>34.111469999999997</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>7.3136539999999997</v>
+        <v>34.13879</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>7.3198590000000001</v>
+        <v>34.166379999999997</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>7.3260459999999998</v>
+        <v>34.19417</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>7.3321730000000001</v>
+        <v>34.222140000000003</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>7.3382139999999998</v>
+        <v>34.250300000000003</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>7.3441450000000001</v>
+        <v>34.278619999999997</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>7.3499689999999998</v>
+        <v>34.307070000000003</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>7.3556749999999997</v>
+        <v>34.335650000000001</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>7.3612469999999997</v>
+        <v>34.364330000000002</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>7.3662109999999998</v>
+        <v>34.39038</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>7.3699450000000004</v>
+        <v>34.411299999999997</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>7.3724600000000002</v>
+        <v>34.42736</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>7.3737599999999999</v>
+        <v>34.438789999999997</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>7.3738520000000003</v>
+        <v>34.445709999999998</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>7.3727499999999999</v>
+        <v>34.448210000000003</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>7.3704770000000002</v>
+        <v>34.446370000000002</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>7.367019</v>
+        <v>34.44023</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>7.3623659999999997</v>
+        <v>34.429819999999999</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>7.356509</v>
+        <v>34.41516</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>7.3494260000000002</v>
+        <v>34.396239999999999</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>7.3411299999999997</v>
+        <v>34.373060000000002</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>7.331607</v>
+        <v>34.345590000000001</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>7.320837</v>
+        <v>34.313830000000003</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>7.3088179999999996</v>
+        <v>34.277830000000002</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>7.2955540000000001</v>
+        <v>34.237589999999997</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>7.2810680000000003</v>
+        <v>34.193129999999996</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>7.265924</v>
+        <v>34.146799999999999</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>7.2506360000000001</v>
+        <v>34.100920000000002</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>7.2351960000000002</v>
+        <v>34.05536</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>7.2196239999999996</v>
+        <v>34.010100000000001</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>7.203932</v>
+        <v>33.965139999999998</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>7.1881839999999997</v>
+        <v>33.920560000000002</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>7.1724360000000003</v>
+        <v>33.876460000000002</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>7.1567220000000002</v>
+        <v>33.832920000000001</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>7.1411199999999999</v>
+        <v>33.790050000000001</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>7.1256820000000003</v>
+        <v>33.748010000000001</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>7.1104589999999996</v>
+        <v>33.70693</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>7.095529</v>
+        <v>33.666969999999999</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>7.08094</v>
+        <v>33.628279999999997</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>7.0667350000000004</v>
+        <v>33.59102</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>7.052962</v>
+        <v>33.555370000000003</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>7.0396660000000004</v>
+        <v>33.521430000000002</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>7.0269659999999998</v>
+        <v>33.4893</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>7.0149699999999999</v>
+        <v>33.459069999999997</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>7.003698</v>
+        <v>33.430799999999998</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>6.9934950000000002</v>
+        <v>33.404919999999997</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>6.984483</v>
+        <v>33.381590000000003</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>6.9766469999999998</v>
+        <v>33.360779999999998</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>6.9702830000000002</v>
+        <v>33.342849999999999</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>6.9653910000000003</v>
+        <v>33.327750000000002</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>6.9619970000000002</v>
+        <v>33.315449999999998</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>6.9603020000000004</v>
+        <v>33.306019999999997</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>6.9602199999999996</v>
+        <v>33.299390000000002</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>6.9616949999999997</v>
+        <v>33.295499999999997</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>6.9646869999999996</v>
+        <v>33.2943</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>6.9691650000000003</v>
+        <v>33.295769999999997</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>6.9750319999999997</v>
+        <v>33.299770000000002</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>6.9822220000000002</v>
+        <v>33.306159999999998</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>6.99071</v>
+        <v>33.314830000000001</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>7.0003000000000002</v>
+        <v>33.325600000000001</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>7.0109240000000002</v>
+        <v>33.338380000000001</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>7.0225270000000002</v>
+        <v>33.353099999999998</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>7.0346279999999997</v>
+        <v>33.369250000000001</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>7.0472989999999998</v>
+        <v>33.386839999999999</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>7.060473</v>
+        <v>33.405790000000003</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>7.0738909999999997</v>
+        <v>33.425829999999998</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>7.0875719999999998</v>
+        <v>33.446890000000003</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>7.101343</v>
+        <v>33.468640000000001</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>7.1150450000000003</v>
+        <v>33.490839999999999</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>7.1287159999999998</v>
+        <v>33.513550000000002</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>7.1419370000000004</v>
+        <v>33.536569999999998</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>7.1546310000000002</v>
+        <v>33.559829999999998</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>7.1669010000000002</v>
+        <v>33.583379999999998</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>7.1785410000000001</v>
+        <v>33.606859999999998</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>7.189629</v>
+        <v>33.630290000000002</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>7.2002059999999997</v>
+        <v>33.653669999999998</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>7.2101629999999997</v>
+        <v>33.676810000000003</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>7.219538</v>
+        <v>33.699779999999997</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>7.2282299999999999</v>
+        <v>33.722549999999998</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>7.2360959999999999</v>
+        <v>33.745010000000001</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>7.2432530000000002</v>
+        <v>33.767209999999999</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>7.249873</v>
+        <v>33.789169999999999</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>7.2560289999999998</v>
+        <v>33.810949999999998</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>7.2617039999999999</v>
+        <v>33.83258</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>7.2669030000000001</v>
+        <v>33.854210000000002</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>7.2716459999999996</v>
+        <v>33.875819999999997</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>7.2759689999999999</v>
+        <v>33.897370000000002</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>7.2802379999999998</v>
+        <v>33.919159999999998</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>7.2844119999999997</v>
+        <v>33.941160000000004</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>7.2885749999999998</v>
+        <v>33.963450000000002</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>7.2929909999999998</v>
+        <v>33.986269999999998</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>7.2975729999999999</v>
+        <v>34.009540000000001</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5.xlsx
+++ b/inputs/data_symbols_TD/09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE52137-A38E-4C85-9E5D-851FA496E29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B706B70-62DC-403A-957A-0168BF6017A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{8B319E7E-412A-4583-8BB2-F46E854D6610}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5B9EB345-9D5F-4277-8FCF-648F1A4D997B}"/>
   </bookViews>
   <sheets>
     <sheet name="09_LTAN06_800km_1213COLD_MX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73319BF-E846-4CF9-A46D-60BC79E426BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21EBBA-2525-4B35-8EAB-B7317B3E2950}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5.xlsx
+++ b/inputs/data_symbols_TD/09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B706B70-62DC-403A-957A-0168BF6017A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85E0C631-C348-42D1-B982-4084F0BAC981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5B9EB345-9D5F-4277-8FCF-648F1A4D997B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{65504215-9338-41C6-B27D-77F47B9BAE36}"/>
   </bookViews>
   <sheets>
     <sheet name="09_LTAN06_800km_1213COLD_MX_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E21EBBA-2525-4B35-8EAB-B7317B3E2950}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8981CDE1-632C-4D97-AACE-6EA705622252}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
